--- a/Localization/翻译文本/UI.xlsx
+++ b/Localization/翻译文本/UI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>#var</t>
   </si>
@@ -21,6 +21,9 @@
   </si>
   <si>
     <t>lTips1</t>
+  </si>
+  <si>
+    <t>lTips2</t>
   </si>
   <si>
     <t>zh-cn</t>
@@ -87,7 +90,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -109,33 +112,45 @@
       <c r="F1" s="0" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="0" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="G2" s="0" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
-      <c r="D3" s="0" t="s">
-        <v>9</v>
+      <c r="E3" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="0" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
